--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T12:12:39+00:00</t>
+    <t>2024-11-05T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:00:17+00:00</t>
+    <t>2024-11-05T09:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:16:22+00:00</t>
+    <t>2024-11-05T10:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T10:26:22+00:00</t>
+    <t>2024-11-06T09:40:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T09:40:37+00:00</t>
+    <t>2024-11-07T06:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T06:21:30+00:00</t>
+    <t>2024-11-07T13:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T13:12:32+00:00</t>
+    <t>2024-11-07T14:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T14:31:26+00:00</t>
+    <t>2024-11-08T06:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
+++ b/r5-ELGA-MOPED-187-use-case-description-aufnehmen/ValueSet-moped-AbrechnungsRelevanz-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:16:09+00:00</t>
+    <t>2024-11-12T07:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
